--- a/GunfireDungeon_Godot/excel/ActivityBase@游戏物体注册表.xlsx
+++ b/GunfireDungeon_Godot/excel/ActivityBase@游戏物体注册表.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27855" windowHeight="14280"/>
+    <workbookView windowWidth="24765" windowHeight="12495"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="267">
   <si>
     <t>Id</t>
   </si>
@@ -490,7 +490,10 @@
     <t>res://prefab/part/PartProp.tscn</t>
   </si>
   <si>
-    <t>鞋子-prop0001</t>
+    <t>prop0001</t>
+  </si>
+  <si>
+    <t>鞋子</t>
   </si>
   <si>
     <t>提高移动速度</t>
@@ -505,6 +508,9 @@
     <t>res://resource/sprite/prop/buff/BuffProp0001.png</t>
   </si>
   <si>
+    <t>prop0002</t>
+  </si>
+  <si>
     <t>心之容器</t>
   </si>
   <si>
@@ -514,6 +520,9 @@
     <t>res://resource/sprite/prop/buff/BuffProp0002.png</t>
   </si>
   <si>
+    <t>prop0003</t>
+  </si>
+  <si>
     <t>护盾</t>
   </si>
   <si>
@@ -523,6 +532,9 @@
     <t>res://resource/sprite/prop/buff/BuffProp0003.png</t>
   </si>
   <si>
+    <t>prop0004</t>
+  </si>
+  <si>
     <t>护盾计时器</t>
   </si>
   <si>
@@ -532,6 +544,9 @@
     <t>res://resource/sprite/prop/buff/BuffProp0004.png</t>
   </si>
   <si>
+    <t>prop0005</t>
+  </si>
+  <si>
     <t>杀伤弹</t>
   </si>
   <si>
@@ -541,6 +556,9 @@
     <t>res://resource/sprite/prop/buff/BuffProp0005.png</t>
   </si>
   <si>
+    <t>prop0006</t>
+  </si>
+  <si>
     <t>红宝石戒指</t>
   </si>
   <si>
@@ -550,6 +568,9 @@
     <t>res://resource/sprite/prop/buff/BuffProp0006.png</t>
   </si>
   <si>
+    <t>prop0007</t>
+  </si>
+  <si>
     <t>备用护盾</t>
   </si>
   <si>
@@ -559,6 +580,9 @@
     <t>res://resource/sprite/prop/buff/BuffProp0007.png</t>
   </si>
   <si>
+    <t>prop0008</t>
+  </si>
+  <si>
     <t>眼镜</t>
   </si>
   <si>
@@ -568,6 +592,9 @@
     <t>res://resource/sprite/prop/buff/BuffProp0008.png</t>
   </si>
   <si>
+    <t>prop0009</t>
+  </si>
+  <si>
     <t>高速子弹</t>
   </si>
   <si>
@@ -577,6 +604,9 @@
     <t>res://resource/sprite/prop/buff/BuffProp0009.png</t>
   </si>
   <si>
+    <t>prop0010</t>
+  </si>
+  <si>
     <t>分裂子弹</t>
   </si>
   <si>
@@ -586,6 +616,9 @@
     <t>res://resource/sprite/prop/buff/BuffProp0010.png</t>
   </si>
   <si>
+    <t>prop0011</t>
+  </si>
+  <si>
     <t>弹射子弹</t>
   </si>
   <si>
@@ -595,6 +628,9 @@
     <t>res://resource/sprite/prop/buff/BuffProp0011.png</t>
   </si>
   <si>
+    <t>prop0012</t>
+  </si>
+  <si>
     <t>穿透子弹</t>
   </si>
   <si>
@@ -604,6 +640,9 @@
     <t>res://resource/sprite/prop/buff/BuffProp0012.png</t>
   </si>
   <si>
+    <t>prop0013</t>
+  </si>
+  <si>
     <t>武器背包</t>
   </si>
   <si>
@@ -613,6 +652,9 @@
     <t>res://resource/sprite/prop/buff/BuffProp0013.png</t>
   </si>
   <si>
+    <t>prop0014</t>
+  </si>
+  <si>
     <t>道具背包</t>
   </si>
   <si>
@@ -622,7 +664,10 @@
     <t>res://resource/sprite/prop/buff/BuffProp0014.png</t>
   </si>
   <si>
-    <t>医药箱-prop5000</t>
+    <t>prop5000</t>
+  </si>
+  <si>
+    <t>医药箱</t>
   </si>
   <si>
     <t>使用后回复一颗红心</t>
@@ -634,6 +679,9 @@
     <t>res://resource/sprite/prop/active/ActiveProp5000.png</t>
   </si>
   <si>
+    <t>prop5001</t>
+  </si>
+  <si>
     <t>弹药箱</t>
   </si>
   <si>
@@ -643,6 +691,9 @@
     <t>res://resource/sprite/prop/active/ActiveProp5001.png</t>
   </si>
   <si>
+    <t>prop5002</t>
+  </si>
+  <si>
     <t>猪猪存钱罐</t>
   </si>
   <si>
@@ -652,6 +703,9 @@
     <t>res://resource/sprite/prop/active/ActiveProp5002.png</t>
   </si>
   <si>
+    <t>prop5003</t>
+  </si>
+  <si>
     <t>红外遥控器</t>
   </si>
   <si>
@@ -661,6 +715,9 @@
     <t>res://resource/sprite/prop/active/ActiveProp5003.png</t>
   </si>
   <si>
+    <t>prop5004</t>
+  </si>
+  <si>
     <t>魔术棒</t>
   </si>
   <si>
@@ -670,6 +727,9 @@
     <t>res://resource/sprite/prop/active/ActiveProp5004.png</t>
   </si>
   <si>
+    <t>prop5005</t>
+  </si>
+  <si>
     <t>便携式供血器</t>
   </si>
   <si>
@@ -677,6 +737,9 @@
   </si>
   <si>
     <t>res://resource/sprite/prop/active/ActiveProp5005.png</t>
+  </si>
+  <si>
+    <t>prop5006</t>
   </si>
   <si>
     <t>便携式献血器</t>
@@ -2828,9 +2891,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="1:13">
+      <c r="A60" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="B60" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C60" s="1">
         <v>9</v>
@@ -2839,28 +2905,30 @@
         <v>4</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H60" s="1" t="b">
         <v>0</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K60" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M60" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:13">
-      <c r="A61" s="1"/>
+      <c r="A61" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="B61" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C61" s="1">
         <v>9</v>
@@ -2870,7 +2938,7 @@
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="1" t="b">
@@ -2878,19 +2946,21 @@
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K61" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M61" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:13">
-      <c r="A62" s="1"/>
+      <c r="A62" s="3" t="s">
+        <v>155</v>
+      </c>
       <c r="B62" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C62" s="1">
         <v>9</v>
@@ -2900,7 +2970,7 @@
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G62" s="2"/>
       <c r="H62" s="1" t="b">
@@ -2908,19 +2978,21 @@
       </c>
       <c r="I62" s="1"/>
       <c r="J62" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K62" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="M62" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:13">
-      <c r="A63" s="1"/>
+      <c r="A63" s="3" t="s">
+        <v>159</v>
+      </c>
       <c r="B63" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C63" s="1">
         <v>9</v>
@@ -2930,7 +3002,7 @@
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G63" s="2"/>
       <c r="H63" s="1" t="b">
@@ -2938,19 +3010,21 @@
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K63" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="M63" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:13">
-      <c r="A64" s="1"/>
+      <c r="A64" s="3" t="s">
+        <v>163</v>
+      </c>
       <c r="B64" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C64" s="1">
         <v>9</v>
@@ -2960,7 +3034,7 @@
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G64" s="2"/>
       <c r="H64" s="1" t="b">
@@ -2968,19 +3042,21 @@
       </c>
       <c r="I64" s="1"/>
       <c r="J64" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K64" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="M64" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:13">
-      <c r="A65" s="1"/>
+      <c r="A65" s="3" t="s">
+        <v>167</v>
+      </c>
       <c r="B65" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C65" s="1">
         <v>9</v>
@@ -2990,7 +3066,7 @@
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="G65" s="2"/>
       <c r="H65" s="1" t="b">
@@ -2998,19 +3074,21 @@
       </c>
       <c r="I65" s="1"/>
       <c r="J65" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K65" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="M65" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:13">
-      <c r="A66" s="1"/>
+      <c r="A66" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="B66" s="1" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C66" s="1">
         <v>9</v>
@@ -3020,7 +3098,7 @@
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="1" t="b">
@@ -3028,19 +3106,21 @@
       </c>
       <c r="I66" s="1"/>
       <c r="J66" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K66" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="M66" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:13">
-      <c r="A67" s="1"/>
+      <c r="A67" s="3" t="s">
+        <v>175</v>
+      </c>
       <c r="B67" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="C67" s="1">
         <v>9</v>
@@ -3050,7 +3130,7 @@
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="1" t="b">
@@ -3058,19 +3138,21 @@
       </c>
       <c r="I67" s="1"/>
       <c r="J67" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K67" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="M67" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:13">
-      <c r="A68" s="1"/>
+      <c r="A68" s="3" t="s">
+        <v>179</v>
+      </c>
       <c r="B68" s="1" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C68" s="1">
         <v>9</v>
@@ -3080,7 +3162,7 @@
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="1" t="b">
@@ -3088,19 +3170,21 @@
       </c>
       <c r="I68" s="1"/>
       <c r="J68" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K68" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="M68" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="69" customFormat="1" ht="27" spans="1:13">
-      <c r="A69" s="1"/>
+      <c r="A69" s="1" t="s">
+        <v>183</v>
+      </c>
       <c r="B69" s="1" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C69" s="1">
         <v>9</v>
@@ -3110,7 +3194,7 @@
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="2" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="1" t="b">
@@ -3118,19 +3202,21 @@
       </c>
       <c r="I69" s="1"/>
       <c r="J69" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K69" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="M69" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:13">
-      <c r="A70" s="1"/>
+      <c r="A70" s="1" t="s">
+        <v>187</v>
+      </c>
       <c r="B70" s="1" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C70" s="1">
         <v>9</v>
@@ -3140,7 +3226,7 @@
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="2" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="1" t="b">
@@ -3148,19 +3234,21 @@
       </c>
       <c r="I70" s="1"/>
       <c r="J70" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K70" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="M70" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="71" customFormat="1" spans="1:13">
-      <c r="A71" s="1"/>
+      <c r="A71" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="B71" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="C71" s="1">
         <v>9</v>
@@ -3170,7 +3258,7 @@
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="2" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="1" t="b">
@@ -3178,19 +3266,21 @@
       </c>
       <c r="I71" s="1"/>
       <c r="J71" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K71" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="M71" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="72" customFormat="1" spans="1:13">
-      <c r="A72" s="1"/>
+      <c r="A72" s="1" t="s">
+        <v>195</v>
+      </c>
       <c r="B72" s="1" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="C72" s="1">
         <v>9</v>
@@ -3200,7 +3290,7 @@
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="2" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="1" t="b">
@@ -3208,19 +3298,21 @@
       </c>
       <c r="I72" s="1"/>
       <c r="J72" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K72" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="M72" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="73" customFormat="1" spans="1:13">
-      <c r="A73" s="1"/>
+      <c r="A73" s="1" t="s">
+        <v>199</v>
+      </c>
       <c r="B73" s="1" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="C73" s="1">
         <v>9</v>
@@ -3230,7 +3322,7 @@
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="1" t="b">
@@ -3238,10 +3330,10 @@
       </c>
       <c r="I73" s="1"/>
       <c r="J73" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K73" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="M73" s="2" t="b">
         <v>1</v>
@@ -3287,9 +3379,11 @@
       <c r="M76" s="2"/>
     </row>
     <row r="78" customFormat="1" spans="1:13">
-      <c r="A78" s="1"/>
+      <c r="A78" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="B78" s="1" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="C78" s="1">
         <v>9</v>
@@ -3299,7 +3393,7 @@
       </c>
       <c r="E78" s="1"/>
       <c r="F78" s="2" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="1" t="b">
@@ -3307,19 +3401,21 @@
       </c>
       <c r="I78" s="1"/>
       <c r="J78" s="3" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="K78" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="M78" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="79" customFormat="1" spans="1:13">
-      <c r="A79" s="1"/>
+      <c r="A79" s="1" t="s">
+        <v>208</v>
+      </c>
       <c r="B79" s="1" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="C79" s="1">
         <v>9</v>
@@ -3329,7 +3425,7 @@
       </c>
       <c r="E79" s="1"/>
       <c r="F79" s="2" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="1" t="b">
@@ -3337,19 +3433,21 @@
       </c>
       <c r="I79" s="1"/>
       <c r="J79" s="3" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="K79" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="M79" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="80" customFormat="1" ht="40.5" spans="1:13">
-      <c r="A80" s="1"/>
+      <c r="A80" s="1" t="s">
+        <v>212</v>
+      </c>
       <c r="B80" s="1" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C80" s="1">
         <v>9</v>
@@ -3359,7 +3457,7 @@
       </c>
       <c r="E80" s="1"/>
       <c r="F80" s="2" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="1" t="b">
@@ -3367,19 +3465,21 @@
       </c>
       <c r="I80" s="1"/>
       <c r="J80" s="3" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="K80" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="M80" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="81" customFormat="1" spans="1:13">
-      <c r="A81" s="1"/>
+      <c r="A81" s="1" t="s">
+        <v>216</v>
+      </c>
       <c r="B81" s="1" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="C81" s="1">
         <v>9</v>
@@ -3389,7 +3489,7 @@
       </c>
       <c r="E81" s="1"/>
       <c r="F81" s="2" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="1" t="b">
@@ -3397,19 +3497,21 @@
       </c>
       <c r="I81" s="1"/>
       <c r="J81" s="3" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="K81" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="M81" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="82" customFormat="1" ht="27" spans="1:13">
-      <c r="A82" s="1"/>
+      <c r="A82" s="1" t="s">
+        <v>220</v>
+      </c>
       <c r="B82" s="2" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="C82" s="1">
         <v>9</v>
@@ -3419,7 +3521,7 @@
       </c>
       <c r="E82" s="1"/>
       <c r="F82" s="2" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="G82" s="2"/>
       <c r="H82" s="1" t="b">
@@ -3427,19 +3529,21 @@
       </c>
       <c r="I82" s="1"/>
       <c r="J82" s="3" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="K82" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="M82" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="1:13">
-      <c r="A83" s="1"/>
+      <c r="A83" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="B83" s="2" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="C83" s="1">
         <v>9</v>
@@ -3449,7 +3553,7 @@
       </c>
       <c r="E83" s="1"/>
       <c r="F83" s="2" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="1" t="b">
@@ -3457,19 +3561,21 @@
       </c>
       <c r="I83" s="1"/>
       <c r="J83" s="3" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="K83" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="M83" s="2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="1:13">
-      <c r="A84" s="1"/>
+      <c r="A84" s="1" t="s">
+        <v>228</v>
+      </c>
       <c r="B84" s="2" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="C84" s="1">
         <v>9</v>
@@ -3479,7 +3585,7 @@
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="2" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="1" t="b">
@@ -3487,10 +3593,10 @@
       </c>
       <c r="I84" s="1"/>
       <c r="J84" s="3" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="K84" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="M84" s="2" t="b">
         <v>1</v>
@@ -3524,25 +3630,25 @@
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="1" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="C87" s="1">
         <v>10</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="H87" s="1" t="b">
         <v>0</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="K87" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="M87" t="b">
         <v>1</v>
@@ -3563,159 +3669,159 @@
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="1" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="C90" s="1">
         <v>99</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="H90" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="1" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="C91" s="1">
         <v>99</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="H91" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="1" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="C92" s="1">
         <v>99</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="H92" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="1" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="C93" s="1">
         <v>99</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="H93" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="1" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="C95" s="1">
         <v>99</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="H95" s="1" t="b">
         <v>0</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="K95" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="1" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="C96" s="1">
         <v>99</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="H96" s="1" t="b">
         <v>0</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="K96" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="1" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="C97" s="1">
         <v>99</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="H97" s="1" t="b">
         <v>0</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="K97" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="1" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="C99" s="1">
         <v>99</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="H99" s="1" t="b">
         <v>0</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
     </row>
     <row r="107" customFormat="1" spans="1:10">

--- a/GunfireDungeon_Godot/excel/ActivityBase@游戏物体注册表.xlsx
+++ b/GunfireDungeon_Godot/excel/ActivityBase@游戏物体注册表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24765" windowHeight="12495"/>
+    <workbookView windowHeight="18800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1853,19 +1853,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:M130"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="22.425" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.4333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.6" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.4230769230769" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.4326923076923" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5961538461538" style="1" customWidth="1"/>
     <col min="4" max="5" width="27.375" style="1" customWidth="1"/>
-    <col min="6" max="7" width="35.5583333333333" style="2" customWidth="1"/>
-    <col min="8" max="8" width="18.8166666666667" style="1" customWidth="1"/>
+    <col min="6" max="7" width="35.5576923076923" style="2" customWidth="1"/>
+    <col min="8" max="8" width="18.8173076923077" style="1" customWidth="1"/>
     <col min="9" max="9" width="22.125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="63.3666666666667" style="3" customWidth="1"/>
-    <col min="11" max="11" width="61.9166666666667" customWidth="1"/>
-    <col min="12" max="12" width="35.325" customWidth="1"/>
-    <col min="13" max="13" width="32.425" customWidth="1"/>
+    <col min="10" max="10" width="63.3653846153846" style="3" customWidth="1"/>
+    <col min="11" max="11" width="61.9134615384615" customWidth="1"/>
+    <col min="12" max="12" width="35.3269230769231" customWidth="1"/>
+    <col min="13" max="13" width="32.4230769230769" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:13">
@@ -2480,7 +2480,7 @@
       </c>
     </row>
     <row r="31" ht="39" customHeight="1"/>
-    <row r="32" spans="1:10">
+    <row r="32" ht="17" spans="1:10">
       <c r="A32" s="1" t="s">
         <v>96</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" ht="17" spans="1:10">
       <c r="A33" s="1" t="s">
         <v>99</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" customFormat="1" spans="1:10">
+    <row r="34" customFormat="1" ht="17" spans="1:10">
       <c r="A34" s="1" t="s">
         <v>101</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="35" customFormat="1" spans="1:10">
+    <row r="35" customFormat="1" ht="17" spans="1:10">
       <c r="A35" s="1" t="s">
         <v>103</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="36" customFormat="1" spans="1:10">
+    <row r="36" customFormat="1" ht="17" spans="1:10">
       <c r="A36" s="1" t="s">
         <v>107</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="37" customFormat="1" spans="1:10">
+    <row r="37" customFormat="1" ht="17" spans="1:10">
       <c r="A37" s="1" t="s">
         <v>111</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="38" customFormat="1" spans="1:10">
+    <row r="38" customFormat="1" ht="17" spans="1:10">
       <c r="A38" s="1" t="s">
         <v>114</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="39" customFormat="1" spans="1:10">
+    <row r="39" customFormat="1" ht="17" spans="1:10">
       <c r="A39" s="1" t="s">
         <v>116</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="40" customFormat="1" spans="1:10">
+    <row r="40" customFormat="1" ht="17" spans="1:10">
       <c r="A40" s="1" t="s">
         <v>118</v>
       </c>
@@ -2686,7 +2686,7 @@
       <c r="I41" s="4"/>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" customFormat="1" spans="1:10">
+    <row r="42" customFormat="1" ht="17" spans="1:10">
       <c r="A42" s="1" t="s">
         <v>121</v>
       </c>
@@ -2720,7 +2720,7 @@
       <c r="I43" s="4"/>
       <c r="J43" s="3"/>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" ht="17" spans="1:10">
       <c r="A44" s="1" t="s">
         <v>124</v>
       </c>
@@ -2737,7 +2737,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="47" customFormat="1" spans="1:10">
+    <row r="47" customFormat="1" ht="17" spans="1:10">
       <c r="A47" s="1" t="s">
         <v>127</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="48" customFormat="1" spans="1:10">
+    <row r="48" customFormat="1" ht="17" spans="1:10">
       <c r="A48" s="1" t="s">
         <v>130</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" ht="17" spans="1:10">
       <c r="A49" s="1" t="s">
         <v>132</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="50" customFormat="1" spans="1:10">
+    <row r="50" customFormat="1" ht="17" spans="1:10">
       <c r="A50" s="1" t="s">
         <v>134</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" ht="17" spans="1:10">
       <c r="A54" s="1" t="s">
         <v>136</v>
       </c>
@@ -2837,7 +2837,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="55" customFormat="1" spans="1:10">
+    <row r="55" customFormat="1" ht="17" spans="1:10">
       <c r="A55" s="1" t="s">
         <v>139</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="57" customFormat="1" spans="1:13">
+    <row r="57" customFormat="1" ht="17" spans="1:13">
       <c r="A57" s="1" t="s">
         <v>142</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" ht="17" spans="1:13">
       <c r="A60" s="3" t="s">
         <v>145</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" customFormat="1" spans="1:13">
+    <row r="61" customFormat="1" ht="17" spans="1:13">
       <c r="A61" s="3" t="s">
         <v>151</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" customFormat="1" spans="1:13">
+    <row r="62" customFormat="1" ht="17" spans="1:13">
       <c r="A62" s="3" t="s">
         <v>155</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" customFormat="1" spans="1:13">
+    <row r="63" customFormat="1" ht="17" spans="1:13">
       <c r="A63" s="3" t="s">
         <v>159</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" customFormat="1" spans="1:13">
+    <row r="64" customFormat="1" ht="17" spans="1:13">
       <c r="A64" s="3" t="s">
         <v>163</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" customFormat="1" spans="1:13">
+    <row r="65" customFormat="1" ht="17" spans="1:13">
       <c r="A65" s="3" t="s">
         <v>167</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" customFormat="1" spans="1:13">
+    <row r="66" customFormat="1" ht="17" spans="1:13">
       <c r="A66" s="3" t="s">
         <v>171</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" customFormat="1" spans="1:13">
+    <row r="67" customFormat="1" ht="17" spans="1:13">
       <c r="A67" s="3" t="s">
         <v>175</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" customFormat="1" spans="1:13">
+    <row r="68" customFormat="1" ht="17" spans="1:13">
       <c r="A68" s="3" t="s">
         <v>179</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" customFormat="1" ht="27" spans="1:13">
+    <row r="69" customFormat="1" ht="34" spans="1:13">
       <c r="A69" s="1" t="s">
         <v>183</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" customFormat="1" spans="1:13">
+    <row r="70" customFormat="1" ht="17" spans="1:13">
       <c r="A70" s="1" t="s">
         <v>187</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" customFormat="1" spans="1:13">
+    <row r="71" customFormat="1" ht="17" spans="1:13">
       <c r="A71" s="1" t="s">
         <v>191</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" customFormat="1" spans="1:13">
+    <row r="72" customFormat="1" ht="17" spans="1:13">
       <c r="A72" s="1" t="s">
         <v>195</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" customFormat="1" spans="1:13">
+    <row r="73" customFormat="1" ht="17" spans="1:13">
       <c r="A73" s="1" t="s">
         <v>199</v>
       </c>
@@ -3378,7 +3378,7 @@
       <c r="J76" s="3"/>
       <c r="M76" s="2"/>
     </row>
-    <row r="78" customFormat="1" spans="1:13">
+    <row r="78" customFormat="1" ht="17" spans="1:13">
       <c r="A78" s="1" t="s">
         <v>203</v>
       </c>
@@ -3410,7 +3410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" customFormat="1" spans="1:13">
+    <row r="79" customFormat="1" ht="17" spans="1:13">
       <c r="A79" s="1" t="s">
         <v>208</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" customFormat="1" ht="40.5" spans="1:13">
+    <row r="80" customFormat="1" ht="51" spans="1:13">
       <c r="A80" s="1" t="s">
         <v>212</v>
       </c>
@@ -3474,7 +3474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" customFormat="1" spans="1:13">
+    <row r="81" customFormat="1" ht="17" spans="1:13">
       <c r="A81" s="1" t="s">
         <v>216</v>
       </c>
@@ -3506,7 +3506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" customFormat="1" ht="27" spans="1:13">
+    <row r="82" customFormat="1" ht="34" spans="1:13">
       <c r="A82" s="1" t="s">
         <v>220</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" customFormat="1" spans="1:13">
+    <row r="83" customFormat="1" ht="17" spans="1:13">
       <c r="A83" s="1" t="s">
         <v>224</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" customFormat="1" spans="1:13">
+    <row r="84" customFormat="1" ht="17" spans="1:13">
       <c r="A84" s="1" t="s">
         <v>228</v>
       </c>
@@ -3628,7 +3628,7 @@
       <c r="J86" s="3"/>
       <c r="M86" s="2"/>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" ht="17" spans="1:13">
       <c r="A87" s="1" t="s">
         <v>232</v>
       </c>
@@ -3667,7 +3667,7 @@
       <c r="J88" s="3"/>
       <c r="M88" s="2"/>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" ht="17" spans="1:10">
       <c r="A90" s="1" t="s">
         <v>236</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" ht="17" spans="1:10">
       <c r="A91" s="1" t="s">
         <v>239</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" ht="17" spans="1:10">
       <c r="A92" s="1" t="s">
         <v>242</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" ht="17" spans="1:10">
       <c r="A93" s="1" t="s">
         <v>245</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" ht="17" spans="1:11">
       <c r="A95" s="1" t="s">
         <v>248</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" ht="17" spans="1:11">
       <c r="A96" s="1" t="s">
         <v>253</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" ht="17" spans="1:11">
       <c r="A97" s="1" t="s">
         <v>258</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" ht="17" spans="1:10">
       <c r="A99" s="1" t="s">
         <v>263</v>
       </c>
@@ -4075,7 +4075,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -4087,7 +4087,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
